--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_47.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6031174.822985777</v>
+        <v>5990833.564147705</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645791</v>
+        <v>6767152.318645787</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645791</v>
+        <v>6767152.318645787</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517478</v>
+        <v>2916902.906517476</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517478</v>
+        <v>2916902.906517476</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37714026.27614527</v>
+        <v>37714026.27614529</v>
       </c>
     </row>
   </sheetData>
@@ -675,10 +675,10 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>522.1267819420522</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K2" t="n">
         <v>97.12488247690055</v>
@@ -687,25 +687,25 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>297.9910820919849</v>
+      </c>
+      <c r="N2" t="n">
         <v>814</v>
       </c>
-      <c r="N2" t="n">
-        <v>194.5855355810472</v>
-      </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>31.55202437320305</v>
       </c>
       <c r="P2" t="n">
         <v>814</v>
       </c>
       <c r="Q2" t="n">
-        <v>781.6028000000002</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
         <v>586.6755817285639</v>
@@ -714,7 +714,7 @@
         <v>649.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>322.4606570412596</v>
+        <v>323.4204155522383</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>323.5464468474237</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>125.5575371970017</v>
       </c>
     </row>
     <row r="4">
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061066</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>297.3920501269228</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>425.4875446583044</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
@@ -900,31 +900,31 @@
         <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690055</v>
+        <v>97.12488247690061</v>
       </c>
       <c r="L5" t="n">
-        <v>650.9664887921592</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
-        <v>297.9910820919849</v>
+        <v>514.0207012252068</v>
       </c>
       <c r="N5" t="n">
         <v>194.5855355810472</v>
@@ -954,7 +954,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>238.3734759809475</v>
+        <v>581.8617076836772</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606677</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>131.9860885083954</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>96.62571193790353</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061022</v>
+        <v>114.9691617061031</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1140,7 +1140,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
         <v>3.75737228701621</v>
@@ -1149,28 +1149,28 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>93.56939138541429</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690055</v>
+        <v>805.7311192831504</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>297.9910820919849</v>
+        <v>814</v>
       </c>
       <c r="N8" t="n">
-        <v>194.5855355810472</v>
+        <v>814.0000000000045</v>
       </c>
       <c r="O8" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>650.9664887921555</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
@@ -1179,16 +1179,16 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>438.3363995050528</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>649.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>147.2737972923793</v>
+        <v>431.9201565853224</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
@@ -1264,13 +1264,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V9" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>147.4266700713387</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.3920501269201</v>
+        <v>297.3920501269282</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>45.57343567650234</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>162.9747707395242</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1425,7 +1425,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.14518808597777</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>67.57968198731129</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>105.8608835496095</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>387.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>341.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>260.3174326828064</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1805,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T17" t="n">
-        <v>307.2449731139783</v>
+        <v>307.6755817285639</v>
       </c>
       <c r="U17" t="n">
         <v>370.2212965486107</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>136.1613870511484</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>339.4016293563777</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7929984536983</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>131.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>124.9326809922826</v>
+        <v>125.3632896068686</v>
       </c>
       <c r="F23" t="n">
         <v>125.8896287080119</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2501,28 +2501,28 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>339.4016293563777</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>36.63518730567526</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2553,16 +2553,16 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>4.07252010553818</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>114.4144878985971</v>
       </c>
       <c r="V26" t="n">
         <v>404.8510241668239</v>
@@ -2708,22 +2708,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2.572420793687929</v>
       </c>
       <c r="H28" t="n">
         <v>3.77112610161862</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2793,19 +2793,19 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>67.5399419805665</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,16 +2844,16 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>332.2189310630618</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>286.3174326828064</v>
@@ -2951,16 +2951,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>3.77112610161862</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>28.84682113613819</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3048,28 +3048,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589756</v>
+        <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320760658</v>
+        <v>727.1079320763263</v>
       </c>
       <c r="L32" t="n">
-        <v>397.7077537618453</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920268</v>
+        <v>256.9910820920259</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810893</v>
+        <v>153.5855355810884</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>397.7077537618804</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579538</v>
+        <v>329.9706110579529</v>
       </c>
       <c r="R32" t="n">
         <v>8.456591385414804</v>
@@ -3215,25 +3215,25 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>123.224984084248</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>71.37347970285543</v>
+        <v>70.05053078767008</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         <v>190.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>166.9311696284081</v>
+        <v>158.4745782429939</v>
       </c>
       <c r="D35" t="n">
         <v>119.3391557398498</v>
@@ -3285,28 +3285,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>757.6173000000483</v>
+        <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>10.23281455293388</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>307.0571520017995</v>
+        <v>727.1079320759846</v>
       </c>
       <c r="M35" t="n">
-        <v>256.991082092034</v>
+        <v>654.6988358539346</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810966</v>
+        <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>757.6173000000481</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="36">
@@ -3458,16 +3458,16 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>109.2047614405202</v>
       </c>
       <c r="P37" t="n">
         <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>108.4418998849671</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3516,34 +3516,34 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H38" t="n">
-        <v>117.0096587035274</v>
+        <v>125.4662500889416</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>757.6173000000554</v>
+        <v>719.3211409439467</v>
       </c>
       <c r="K38" t="n">
-        <v>10.23281455289469</v>
+        <v>56.12488247690055</v>
       </c>
       <c r="L38" t="n">
-        <v>307.057152001807</v>
+        <v>727.1079320760183</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920413</v>
+        <v>256.9910820920404</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811038</v>
+        <v>153.5855355811029</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000553</v>
+        <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3695,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>349.445564079015</v>
+        <v>109.2047614405202</v>
       </c>
       <c r="P40" t="n">
-        <v>156.2070946897827</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>434.839266425598</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>113.9364105579687</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>81.41167584538807</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>90.83375267785861</v>
+        <v>81.90670016750805</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>262.4745782429939</v>
@@ -3981,13 +3981,13 @@
         <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>118.8185513667295</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4029,19 +4029,19 @@
         <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>451.3734759809475</v>
+        <v>108.450022093081</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>324.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4057,10 +4057,10 @@
         <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>110.0801924787765</v>
       </c>
       <c r="E45" t="n">
-        <v>155.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>152.6362423378769</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>16.55705513387049</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4193,7 +4193,7 @@
         <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>702.4077201726793</v>
+        <v>550.8105891800685</v>
       </c>
       <c r="C2" t="n">
-        <v>248.3929946747056</v>
+        <v>96.79586368209488</v>
       </c>
       <c r="D2" t="n">
-        <v>237.9494030182917</v>
+        <v>86.35227202568095</v>
       </c>
       <c r="E2" t="n">
-        <v>233.5420397790304</v>
+        <v>81.94490878641969</v>
       </c>
       <c r="F2" t="n">
-        <v>228.6030208820488</v>
+        <v>77.00588988943801</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8076953396081</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>343.5792101595432</v>
+        <v>65.12</v>
       </c>
       <c r="K2" t="n">
-        <v>1051.333268263684</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L2" t="n">
-        <v>1857.193268263684</v>
+        <v>1578.734058104141</v>
       </c>
       <c r="M2" t="n">
-        <v>1840.831046041462</v>
+        <v>2083.592965081934</v>
       </c>
       <c r="N2" t="n">
-        <v>2450.14</v>
+        <v>2067.230742859711</v>
       </c>
       <c r="O2" t="n">
-        <v>3256</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P2" t="n">
-        <v>3239.637777777778</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S2" t="n">
-        <v>2906.781043807457</v>
+        <v>2756.153365856239</v>
       </c>
       <c r="T2" t="n">
-        <v>2314.179446101837</v>
+        <v>2163.551768150619</v>
       </c>
       <c r="U2" t="n">
-        <v>1658.400358678998</v>
+        <v>1507.77268072778</v>
       </c>
       <c r="V2" t="n">
-        <v>1332.682523283786</v>
+        <v>1181.085392291176</v>
       </c>
       <c r="W2" t="n">
-        <v>1091.901234414142</v>
+        <v>940.3041034215316</v>
       </c>
       <c r="X2" t="n">
-        <v>897.6771602114478</v>
+        <v>746.080029218837</v>
       </c>
       <c r="Y2" t="n">
-        <v>785.2353090166939</v>
+        <v>633.6381780240831</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>429.8673863086054</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="C3" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="D3" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="E3" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="F3" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="H3" t="n">
         <v>65.12</v>
@@ -4421,31 +4421,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1045.724879873102</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>896.9634684666578</v>
+        <v>667.7506049216878</v>
       </c>
       <c r="S3" t="n">
-        <v>829.7271048660403</v>
+        <v>600.5142413210704</v>
       </c>
       <c r="T3" t="n">
-        <v>824.3152208079456</v>
+        <v>595.1023572629756</v>
       </c>
       <c r="U3" t="n">
-        <v>824.1027362016963</v>
+        <v>594.8898726567263</v>
       </c>
       <c r="V3" t="n">
-        <v>809.4454966143022</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W3" t="n">
-        <v>776.7453522609401</v>
+        <v>547.5324887159701</v>
       </c>
       <c r="X3" t="n">
-        <v>756.6819790837809</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="Y3" t="n">
-        <v>756.6819790837809</v>
+        <v>400.6433203903244</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>580.0072084245178</v>
+        <v>1244.656612312233</v>
       </c>
       <c r="C4" t="n">
-        <v>706.0092142429536</v>
+        <v>1370.658618130668</v>
       </c>
       <c r="D4" t="n">
-        <v>819.3283583679537</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="E4" t="n">
-        <v>937.1572625793667</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="F4" t="n">
-        <v>1061.518235171302</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="G4" t="n">
-        <v>1214.924801058188</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.924801058188</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994271</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994271</v>
+        <v>1483.977762255668</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931139</v>
+        <v>1546.422113931145</v>
       </c>
       <c r="L4" t="n">
-        <v>1522.636630943483</v>
+        <v>1546.422113931145</v>
       </c>
       <c r="M4" t="n">
-        <v>1400.786518415655</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1227.872300969508</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O4" t="n">
-        <v>984.9979938189882</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P4" t="n">
-        <v>694.6465823762837</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>365.516010229215</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3702550941731</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>209.2948972788944</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>408.1162901648404</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="W4" t="n">
-        <v>580.0072084245178</v>
+        <v>870.4591829427148</v>
       </c>
       <c r="X4" t="n">
-        <v>580.0072084245178</v>
+        <v>1021.489973966908</v>
       </c>
       <c r="Y4" t="n">
-        <v>580.0072084245178</v>
+        <v>1132.899274645941</v>
       </c>
     </row>
     <row r="5">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1510.488528253487</v>
+        <v>1106.448124213083</v>
       </c>
       <c r="C5" t="n">
-        <v>1460.514206795918</v>
+        <v>1056.473802755514</v>
       </c>
       <c r="D5" t="n">
-        <v>1046.0302110991</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E5" t="n">
         <v>637.5824438194345</v>
@@ -4549,7 +4549,7 @@
         <v>632.6434249224528</v>
       </c>
       <c r="G5" t="n">
-        <v>224.8076953396081</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4558,19 +4558,19 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>772.8740581041409</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L5" t="n">
-        <v>921.192150233273</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M5" t="n">
-        <v>1426.051057211066</v>
+        <v>1426.05105721107</v>
       </c>
       <c r="N5" t="n">
-        <v>2035.360011169604</v>
+        <v>2035.360011169608</v>
       </c>
       <c r="O5" t="n">
         <v>2018.997788947385</v>
@@ -4597,13 +4597,13 @@
         <v>2487.721141165332</v>
       </c>
       <c r="W5" t="n">
-        <v>2246.939852295688</v>
+        <v>1899.982042494951</v>
       </c>
       <c r="X5" t="n">
-        <v>2052.715778092993</v>
+        <v>1705.757968292256</v>
       </c>
       <c r="Y5" t="n">
-        <v>1940.273926898239</v>
+        <v>1593.316117097502</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527.4691155388109</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>527.4691155388109</v>
+        <v>65.12</v>
       </c>
       <c r="D6" t="n">
-        <v>527.4691155388109</v>
+        <v>65.12</v>
       </c>
       <c r="E6" t="n">
-        <v>527.4691155388109</v>
+        <v>65.12</v>
       </c>
       <c r="F6" t="n">
-        <v>394.1498342171994</v>
+        <v>65.12</v>
       </c>
       <c r="G6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.552420368536</v>
+        <v>1122.95069113833</v>
       </c>
       <c r="R6" t="n">
-        <v>1071.791008962092</v>
+        <v>974.1892797318864</v>
       </c>
       <c r="S6" t="n">
-        <v>1004.554645361474</v>
+        <v>906.9529161312689</v>
       </c>
       <c r="T6" t="n">
-        <v>999.1427613033796</v>
+        <v>901.5410320731742</v>
       </c>
       <c r="U6" t="n">
-        <v>998.9302766971304</v>
+        <v>901.3285474669249</v>
       </c>
       <c r="V6" t="n">
-        <v>984.2730371097363</v>
+        <v>886.6713078795308</v>
       </c>
       <c r="W6" t="n">
-        <v>951.5728927563741</v>
+        <v>449.9307594857645</v>
       </c>
       <c r="X6" t="n">
-        <v>527.4691155388109</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y6" t="n">
-        <v>527.4691155388109</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,37 +4692,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>611.2083476291953</v>
+        <v>410.4906232651222</v>
       </c>
       <c r="C7" t="n">
-        <v>611.2083476291953</v>
+        <v>536.492629083558</v>
       </c>
       <c r="D7" t="n">
-        <v>611.2083476291953</v>
+        <v>649.8117732085581</v>
       </c>
       <c r="E7" t="n">
-        <v>611.2083476291953</v>
+        <v>767.6406774199711</v>
       </c>
       <c r="F7" t="n">
-        <v>611.2083476291953</v>
+        <v>892.0016500119066</v>
       </c>
       <c r="G7" t="n">
-        <v>764.6149135160805</v>
+        <v>1045.408215898792</v>
       </c>
       <c r="H7" t="n">
-        <v>934.131498675478</v>
+        <v>1214.92480105819</v>
       </c>
       <c r="I7" t="n">
-        <v>1155.264377611561</v>
+        <v>1436.057679994273</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994272</v>
+        <v>1436.057679994273</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="M7" t="n">
         <v>1430.29164756134</v>
@@ -4755,13 +4755,13 @@
         <v>65.12</v>
       </c>
       <c r="W7" t="n">
-        <v>237.0109182596774</v>
+        <v>65.12</v>
       </c>
       <c r="X7" t="n">
-        <v>388.0417092838709</v>
+        <v>216.1507910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>499.4510099629032</v>
+        <v>327.5600917032258</v>
       </c>
     </row>
     <row r="8">
@@ -4771,46 +4771,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241.2847218926082</v>
+        <v>702.4077201726793</v>
       </c>
       <c r="C8" t="n">
-        <v>191.3104004350386</v>
+        <v>652.4333987151097</v>
       </c>
       <c r="D8" t="n">
-        <v>180.8668087786247</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E8" t="n">
-        <v>176.4594455393634</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F8" t="n">
-        <v>171.5204266423818</v>
+        <v>228.6030208820488</v>
       </c>
       <c r="G8" t="n">
-        <v>167.7251010999411</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H8" t="n">
-        <v>159.6345367529437</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I8" t="n">
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>772.8740581041409</v>
+        <v>440.0022333918344</v>
       </c>
       <c r="L8" t="n">
-        <v>1578.734058104141</v>
+        <v>1245.862233391834</v>
       </c>
       <c r="M8" t="n">
-        <v>2083.592965081934</v>
+        <v>1229.500011169612</v>
       </c>
       <c r="N8" t="n">
-        <v>2692.901919040472</v>
+        <v>1213.137788947385</v>
       </c>
       <c r="O8" t="n">
-        <v>2676.539696818249</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4822,25 +4822,25 @@
         <v>3256</v>
       </c>
       <c r="S8" t="n">
-        <v>3160.193769896644</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T8" t="n">
-        <v>2971.632576231427</v>
+        <v>2220.634362390286</v>
       </c>
       <c r="U8" t="n">
-        <v>2315.853488808588</v>
+        <v>1564.855274967447</v>
       </c>
       <c r="V8" t="n">
-        <v>1679.640333084524</v>
+        <v>1332.682523283786</v>
       </c>
       <c r="W8" t="n">
-        <v>1438.85904421488</v>
+        <v>1091.901234414142</v>
       </c>
       <c r="X8" t="n">
-        <v>1244.634970012185</v>
+        <v>897.6771602114478</v>
       </c>
       <c r="Y8" t="n">
-        <v>728.152714777027</v>
+        <v>785.2353090166939</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>411.2534315372855</v>
+        <v>65.12</v>
       </c>
       <c r="C9" t="n">
-        <v>411.2534315372855</v>
+        <v>65.12</v>
       </c>
       <c r="D9" t="n">
-        <v>411.2534315372855</v>
+        <v>65.12</v>
       </c>
       <c r="E9" t="n">
         <v>65.12</v>
@@ -4895,31 +4895,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1071.791008962092</v>
+        <v>609.4418934232809</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.554645361474</v>
+        <v>542.2055298226635</v>
       </c>
       <c r="T9" t="n">
-        <v>999.1427613033796</v>
+        <v>536.7936457645687</v>
       </c>
       <c r="U9" t="n">
-        <v>998.9302766971304</v>
+        <v>132.5407571179154</v>
       </c>
       <c r="V9" t="n">
-        <v>580.2326330693322</v>
+        <v>117.8835175305213</v>
       </c>
       <c r="W9" t="n">
-        <v>431.3168047144446</v>
+        <v>85.18337317715914</v>
       </c>
       <c r="X9" t="n">
-        <v>411.2534315372855</v>
+        <v>65.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>411.2534315372855</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>520.8550572019858</v>
+        <v>895.3945020249623</v>
       </c>
       <c r="C10" t="n">
-        <v>646.8570630204216</v>
+        <v>1021.396507843398</v>
       </c>
       <c r="D10" t="n">
-        <v>760.1762071454217</v>
+        <v>1134.715651968398</v>
       </c>
       <c r="E10" t="n">
-        <v>878.0051113568347</v>
+        <v>1252.544556179811</v>
       </c>
       <c r="F10" t="n">
-        <v>1002.36608394877</v>
+        <v>1376.905528771747</v>
       </c>
       <c r="G10" t="n">
-        <v>1155.772649835656</v>
+        <v>1376.905528771747</v>
       </c>
       <c r="H10" t="n">
-        <v>1325.289234995053</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="I10" t="n">
-        <v>1546.422113931136</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="J10" t="n">
-        <v>1546.422113931136</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931136</v>
+        <v>1546.422113931144</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.63663094348</v>
+        <v>1522.636630943488</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415652</v>
+        <v>1400.78651841566</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.872300969506</v>
+        <v>1227.872300969514</v>
       </c>
       <c r="O10" t="n">
-        <v>984.9979938189855</v>
+        <v>984.9979938189937</v>
       </c>
       <c r="P10" t="n">
-        <v>694.646582376281</v>
+        <v>694.6465823762892</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292123</v>
+        <v>365.5160102292205</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
@@ -4986,19 +4986,19 @@
         <v>253.1956791588049</v>
       </c>
       <c r="U10" t="n">
-        <v>297.6884188566615</v>
+        <v>301.5155525340145</v>
       </c>
       <c r="V10" t="n">
-        <v>297.6884188566615</v>
+        <v>500.3369454199605</v>
       </c>
       <c r="W10" t="n">
-        <v>297.6884188566615</v>
+        <v>672.2278636796379</v>
       </c>
       <c r="X10" t="n">
-        <v>297.6884188566615</v>
+        <v>672.2278636796379</v>
       </c>
       <c r="Y10" t="n">
-        <v>409.0977195356937</v>
+        <v>783.6371643586702</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1071.703323491675</v>
+        <v>1191.434223980582</v>
       </c>
       <c r="C11" t="n">
-        <v>844.9613252664287</v>
+        <v>964.6922257553354</v>
       </c>
       <c r="D11" t="n">
-        <v>657.750056842338</v>
+        <v>777.4809573312447</v>
       </c>
       <c r="E11" t="n">
-        <v>476.5750168354</v>
+        <v>596.3059173243066</v>
       </c>
       <c r="F11" t="n">
-        <v>430.5412434247916</v>
+        <v>414.5992216596482</v>
       </c>
       <c r="G11" t="n">
         <v>249.9782411146742</v>
@@ -5044,13 +5044,13 @@
         <v>2482.844308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
@@ -5068,16 +5068,16 @@
         <v>2528.779734162396</v>
       </c>
       <c r="V11" t="n">
-        <v>2119.839305711059</v>
+        <v>2528.779734162396</v>
       </c>
       <c r="W11" t="n">
-        <v>1702.290340073738</v>
+        <v>2111.230768525075</v>
       </c>
       <c r="X11" t="n">
-        <v>1331.298589103367</v>
+        <v>1740.239017554704</v>
       </c>
       <c r="Y11" t="n">
-        <v>1331.298589103367</v>
+        <v>1451.029489592273</v>
       </c>
     </row>
     <row r="12">
@@ -5117,16 +5117,16 @@
         <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.840378378698</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.670920121557</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1990.525502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2248.493656412844</v>
+        <v>2452.317953866594</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5196,10 +5196,10 @@
         <v>409.3389893823512</v>
       </c>
       <c r="L13" t="n">
-        <v>363.737789295505</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="M13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="N13" t="n">
         <v>65.12</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>653.4059340138207</v>
+        <v>998.1350587215657</v>
       </c>
       <c r="C14" t="n">
-        <v>452.9265620512006</v>
+        <v>797.6556867589455</v>
       </c>
       <c r="D14" t="n">
-        <v>291.9779198897361</v>
+        <v>636.7070445974811</v>
       </c>
       <c r="E14" t="n">
-        <v>291.9779198897361</v>
+        <v>481.7946308531693</v>
       </c>
       <c r="F14" t="n">
-        <v>291.9779198897361</v>
+        <v>326.3505614511371</v>
       </c>
       <c r="G14" t="n">
-        <v>223.7156148520479</v>
+        <v>172.0501854036459</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5269,25 +5269,25 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1580.686366347868</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>2091.535195076804</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N14" t="n">
-        <v>2704.755514851567</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O14" t="n">
-        <v>2704.755514851567</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="P14" t="n">
-        <v>2817.400904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="Q14" t="n">
         <v>3256</v>
@@ -5311,10 +5311,10 @@
         <v>1494.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1149.68547506269</v>
+        <v>1494.414599770435</v>
       </c>
       <c r="Y14" t="n">
-        <v>886.7385733628859</v>
+        <v>1231.467698070631</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>65.12</v>
+        <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>189.076520175299</v>
+        <v>222.6113981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>378.2693362696824</v>
+        <v>411.8042142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>898.1097978648825</v>
+        <v>847.690984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1232.680339607742</v>
+        <v>1182.261526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1614.45062421531</v>
+        <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
-        <v>2101.983075899029</v>
+        <v>1803.074262473451</v>
       </c>
       <c r="P15" t="n">
-        <v>2214.512420368535</v>
+        <v>2164.093606942957</v>
       </c>
       <c r="Q15" t="n">
         <v>2241.235134503383</v>
@@ -5436,19 +5436,19 @@
         <v>599.0397446017254</v>
       </c>
       <c r="M16" t="n">
-        <v>599.0397446017254</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="N16" t="n">
-        <v>599.0397446017254</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="O16" t="n">
-        <v>599.0397446017254</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="P16" t="n">
-        <v>599.0397446017254</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5509,22 +5509,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>887.4717564436343</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>887.4717564436343</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>1398.320585172569</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>2011.540904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O17" t="n">
-        <v>2011.540904947332</v>
+        <v>3256</v>
       </c>
       <c r="P17" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5533,7 +5533,7 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T17" t="n">
         <v>2727.623089983534</v>
@@ -5585,22 +5585,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>404.4452825072959</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>869.8480986016793</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>1141.198560196879</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M18" t="n">
-        <v>1227.279101939739</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.559386547307</v>
+        <v>930.2355021828749</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.601838231026</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P18" t="n">
         <v>1712.131182700533</v>
@@ -5670,22 +5670,22 @@
         <v>859.3027230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>859.3027230120967</v>
+        <v>721.7659684149771</v>
       </c>
       <c r="M19" t="n">
-        <v>859.3027230120967</v>
+        <v>477.6936336649268</v>
       </c>
       <c r="N19" t="n">
-        <v>859.3027230120967</v>
+        <v>477.6936336649268</v>
       </c>
       <c r="O19" t="n">
-        <v>859.3027230120967</v>
+        <v>477.6936336649268</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3027230120967</v>
+        <v>65.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>407.9499286428058</v>
+        <v>65.12</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5743,25 +5743,25 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>774.8263663478684</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>1285.675195076803</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>1898.895514851567</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O20" t="n">
-        <v>2450.14</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="P20" t="n">
-        <v>3256</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
@@ -5822,22 +5822,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>715.7342142372472</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>987.0846758324474</v>
+        <v>987.0846758324475</v>
       </c>
       <c r="M21" t="n">
         <v>1073.165217575307</v>
       </c>
       <c r="N21" t="n">
-        <v>1206.445502182875</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1445.487953866594</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.131182700533</v>
@@ -5919,10 +5919,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>446.72908934717</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.72908934717</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5956,13 +5956,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180183</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E23" t="n">
         <v>448.6115754530863</v>
@@ -5980,22 +5980,22 @@
         <v>65.12</v>
       </c>
       <c r="J23" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K23" t="n">
-        <v>456.4291130376557</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L23" t="n">
-        <v>456.4291130376557</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M23" t="n">
-        <v>967.2779417665907</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N23" t="n">
-        <v>1205.680904947332</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O23" t="n">
-        <v>2011.540904947332</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>2817.400904947332</v>
@@ -6007,25 +6007,25 @@
         <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6062,16 +6062,16 @@
         <v>250.3313981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>439.5242142372473</v>
+        <v>715.7342142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>710.8746758324473</v>
+        <v>987.0846758324474</v>
       </c>
       <c r="M24" t="n">
-        <v>951.0691019397386</v>
+        <v>1227.279101939739</v>
       </c>
       <c r="N24" t="n">
-        <v>1084.349386547307</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O24" t="n">
         <v>1599.601838231026</v>
@@ -6123,46 +6123,46 @@
         <v>428.7519797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>428.7519797853442</v>
+        <v>426.7510658086204</v>
       </c>
       <c r="F25" t="n">
-        <v>433.3229523772797</v>
+        <v>431.3220384005559</v>
       </c>
       <c r="G25" t="n">
-        <v>466.939518264165</v>
+        <v>464.9386042874412</v>
       </c>
       <c r="H25" t="n">
-        <v>516.6661034235625</v>
+        <v>514.6651894468388</v>
       </c>
       <c r="I25" t="n">
-        <v>618.0089823596454</v>
+        <v>616.0080683829217</v>
       </c>
       <c r="J25" t="n">
-        <v>859.3027230120967</v>
+        <v>857.301809035373</v>
       </c>
       <c r="K25" t="n">
-        <v>859.3027230120967</v>
+        <v>857.301809035373</v>
       </c>
       <c r="L25" t="n">
-        <v>859.3027230120967</v>
+        <v>711.2941038254951</v>
       </c>
       <c r="M25" t="n">
-        <v>859.3027230120967</v>
+        <v>467.2217690754447</v>
       </c>
       <c r="N25" t="n">
-        <v>859.3027230120967</v>
+        <v>467.2217690754447</v>
       </c>
       <c r="O25" t="n">
-        <v>859.3027230120967</v>
+        <v>102.1252397027023</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3027230120967</v>
+        <v>102.1252397027023</v>
       </c>
       <c r="Q25" t="n">
-        <v>407.9499286428058</v>
+        <v>102.1252397027023</v>
       </c>
       <c r="R25" t="n">
-        <v>65.12</v>
+        <v>102.1252397027023</v>
       </c>
       <c r="S25" t="n">
         <v>65.12</v>
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253.1649250963515</v>
+        <v>838.6750023209336</v>
       </c>
       <c r="C26" t="n">
-        <v>249.0512684240907</v>
+        <v>611.9330040956872</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>424.7217356715965</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>243.5466956646584</v>
       </c>
       <c r="F26" t="n">
         <v>61.84</v>
@@ -6220,19 +6220,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>1928.125479385524</v>
+        <v>1050.611171271012</v>
       </c>
       <c r="M26" t="n">
-        <v>2438.974308114459</v>
+        <v>1561.459999999947</v>
       </c>
       <c r="N26" t="n">
-        <v>3052.194627889222</v>
+        <v>1561.459999999947</v>
       </c>
       <c r="O26" t="n">
-        <v>3092</v>
+        <v>2326.729999999974</v>
       </c>
       <c r="P26" t="n">
         <v>3092</v>
@@ -6244,25 +6244,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2793.286094312508</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T26" t="n">
-        <v>2427.957223879615</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="U26" t="n">
-        <v>1999.450863729503</v>
+        <v>2584.960940954085</v>
       </c>
       <c r="V26" t="n">
-        <v>1590.510435278166</v>
+        <v>2176.020512502748</v>
       </c>
       <c r="W26" t="n">
-        <v>1172.961469640845</v>
+        <v>1758.471546865427</v>
       </c>
       <c r="X26" t="n">
-        <v>801.9697186704736</v>
+        <v>1387.479795895056</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>1098.270267932625</v>
       </c>
     </row>
     <row r="27">
@@ -6293,22 +6293,22 @@
         <v>61.84</v>
       </c>
       <c r="I27" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>408.546520175299</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>820.4893362696823</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1314.589797864882</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1623.420339607742</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
         <v>2245.213656412845</v>
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.1515880782802</v>
+        <v>284.0306791955608</v>
       </c>
       <c r="C28" t="n">
-        <v>174.1515880782802</v>
+        <v>235.823359349051</v>
       </c>
       <c r="D28" t="n">
-        <v>174.1515880782802</v>
+        <v>174.6756643434394</v>
       </c>
       <c r="E28" t="n">
-        <v>174.1515880782802</v>
+        <v>118.1292958212611</v>
       </c>
       <c r="F28" t="n">
-        <v>174.1515880782802</v>
+        <v>68.24762312657228</v>
       </c>
       <c r="G28" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="H28" t="n">
-        <v>170.342369793817</v>
+        <v>61.84</v>
       </c>
       <c r="I28" t="n">
-        <v>218.2252487298999</v>
+        <v>109.7228789360829</v>
       </c>
       <c r="J28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="K28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="L28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="M28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="N28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="O28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="S28" t="n">
-        <v>61.84</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="T28" t="n">
-        <v>76.66567915880486</v>
+        <v>312.3822987473391</v>
       </c>
       <c r="U28" t="n">
-        <v>149.9668717970915</v>
+        <v>385.6834913856257</v>
       </c>
       <c r="V28" t="n">
-        <v>175.5382646830375</v>
+        <v>411.2548842715717</v>
       </c>
       <c r="W28" t="n">
-        <v>174.1515880782802</v>
+        <v>409.8682076668144</v>
       </c>
       <c r="X28" t="n">
-        <v>174.1515880782802</v>
+        <v>409.8682076668144</v>
       </c>
       <c r="Y28" t="n">
-        <v>174.1515880782802</v>
+        <v>346.7718916572564</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>288.5819982252464</v>
+        <v>1090.6117136978</v>
       </c>
       <c r="C29" t="n">
-        <v>61.84</v>
+        <v>863.8697154725542</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>676.6584470484635</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>495.4834070415254</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6457,19 +6457,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>1162.855479385524</v>
+        <v>764.0617564436008</v>
       </c>
       <c r="M29" t="n">
-        <v>1673.704308114459</v>
+        <v>1274.910585172536</v>
       </c>
       <c r="N29" t="n">
-        <v>2286.924627889222</v>
+        <v>1888.130904947299</v>
       </c>
       <c r="O29" t="n">
-        <v>2286.924627889222</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>2653.400904947332</v>
@@ -6487,19 +6487,19 @@
         <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>1999.450863729503</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="V29" t="n">
-        <v>1590.510435278166</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="W29" t="n">
-        <v>1172.961469640845</v>
+        <v>2010.408258242294</v>
       </c>
       <c r="X29" t="n">
-        <v>837.3867917993684</v>
+        <v>1639.416507271923</v>
       </c>
       <c r="Y29" t="n">
-        <v>548.1772638369378</v>
+        <v>1350.206979309492</v>
       </c>
     </row>
     <row r="30">
@@ -6533,10 +6533,10 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
         <v>1118.560378378698</v>
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>253.4712907105077</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>253.4712907105077</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>192.3235957048961</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>135.7772271827178</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>85.89555448802895</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>65.64921828446326</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H31" t="n">
+        <v>170.342369793817</v>
+      </c>
+      <c r="I31" t="n">
+        <v>218.2252487298999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="K31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="L31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="M31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="N31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="O31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="P31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>406.0589893823512</v>
+      </c>
+      <c r="R31" t="n">
         <v>61.84</v>
       </c>
-      <c r="I31" t="n">
-        <v>109.7228789360829</v>
-      </c>
-      <c r="J31" t="n">
-        <v>297.5566195885342</v>
-      </c>
-      <c r="K31" t="n">
-        <v>233.3942218096018</v>
-      </c>
-      <c r="L31" t="n">
-        <v>204.2560186417855</v>
-      </c>
-      <c r="M31" t="n">
-        <v>204.2560186417855</v>
-      </c>
-      <c r="N31" t="n">
-        <v>204.2560186417855</v>
-      </c>
-      <c r="O31" t="n">
-        <v>204.2560186417855</v>
-      </c>
-      <c r="P31" t="n">
-        <v>204.2560186417855</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>204.2560186417855</v>
-      </c>
-      <c r="R31" t="n">
-        <v>204.2560186417855</v>
-      </c>
       <c r="S31" t="n">
-        <v>204.2560186417855</v>
+        <v>61.84</v>
       </c>
       <c r="T31" t="n">
-        <v>219.0816978005903</v>
+        <v>76.66567915880486</v>
       </c>
       <c r="U31" t="n">
-        <v>292.382890438877</v>
+        <v>149.9668717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>317.9542833248229</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>316.5676067200657</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="X31" t="n">
-        <v>316.5676067200657</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>253.4712907105077</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6691,22 +6691,22 @@
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637025</v>
+        <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
-        <v>430.9405883765168</v>
+        <v>430.9405883765116</v>
       </c>
       <c r="L32" t="n">
-        <v>794.4855845766731</v>
+        <v>415.4025075684307</v>
       </c>
       <c r="M32" t="n">
-        <v>1300.168632968607</v>
+        <v>921.0855559603644</v>
       </c>
       <c r="N32" t="n">
-        <v>1910.301728341285</v>
+        <v>1531.218651333043</v>
       </c>
       <c r="O32" t="n">
-        <v>2675.571728341327</v>
+        <v>1894.763647533204</v>
       </c>
       <c r="P32" t="n">
         <v>2660.033647533245</v>
@@ -6767,19 +6767,19 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>134.974877967565</v>
+        <v>71.63058051381563</v>
       </c>
       <c r="J33" t="n">
-        <v>258.9313981428639</v>
+        <v>195.5871006891146</v>
       </c>
       <c r="K33" t="n">
-        <v>448.1242142372473</v>
+        <v>384.779916783498</v>
       </c>
       <c r="L33" t="n">
-        <v>719.4746758324475</v>
+        <v>656.1303783786981</v>
       </c>
       <c r="M33" t="n">
-        <v>805.5552175753068</v>
+        <v>742.2109201215574</v>
       </c>
       <c r="N33" t="n">
         <v>1163.581204729126</v>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I34" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="M34" t="n">
-        <v>887.362162737523</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="N34" t="n">
-        <v>887.362162737523</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="O34" t="n">
-        <v>534.3868454859928</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="P34" t="n">
-        <v>133.9344239422782</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="Q34" t="n">
-        <v>133.9344239422782</v>
+        <v>572.6002613826477</v>
       </c>
       <c r="R34" t="n">
-        <v>133.9344239422782</v>
+        <v>132.5981119067375</v>
       </c>
       <c r="S34" t="n">
         <v>61.84</v>
@@ -6891,10 +6891,10 @@
         <v>435.5391829427149</v>
       </c>
       <c r="X34" t="n">
-        <v>478.6599739669085</v>
+        <v>478.6599739669322</v>
       </c>
       <c r="Y34" t="n">
-        <v>482.1592746459407</v>
+        <v>482.1592746459644</v>
       </c>
     </row>
     <row r="35">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
         <v>644.0209141871454</v>
@@ -6928,25 +6928,25 @@
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>61.84</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>771.3406764391781</v>
+        <v>430.0181114556215</v>
       </c>
       <c r="L35" t="n">
-        <v>1226.451937043421</v>
+        <v>415.4025075684375</v>
       </c>
       <c r="M35" t="n">
-        <v>1732.134985435355</v>
+        <v>519.3605521604707</v>
       </c>
       <c r="N35" t="n">
-        <v>2342.268080808033</v>
+        <v>1129.493647533149</v>
       </c>
       <c r="O35" t="n">
-        <v>2326.729999999951</v>
+        <v>1894.763647533197</v>
       </c>
       <c r="P35" t="n">
-        <v>3092</v>
+        <v>2660.033647533245</v>
       </c>
       <c r="Q35" t="n">
         <v>3092</v>
@@ -6973,7 +6973,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7004,13 +7004,13 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>134.974877967565</v>
+        <v>71.6305805138156</v>
       </c>
       <c r="J36" t="n">
-        <v>258.9313981428639</v>
+        <v>195.5871006891145</v>
       </c>
       <c r="K36" t="n">
-        <v>448.1242142372473</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L36" t="n">
         <v>944.220378378698</v>
@@ -7101,13 +7101,13 @@
         <v>1011.831843630703</v>
       </c>
       <c r="O37" t="n">
-        <v>1011.831843630703</v>
+        <v>901.5240037917935</v>
       </c>
       <c r="P37" t="n">
-        <v>611.3794220869881</v>
+        <v>501.0715822480788</v>
       </c>
       <c r="Q37" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R37" t="n">
         <v>61.84</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C38" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D38" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E38" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F38" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G38" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H38" t="n">
         <v>61.84</v>
@@ -7165,25 +7165,25 @@
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>61.84</v>
+        <v>100.5229889455635</v>
       </c>
       <c r="K38" t="n">
-        <v>771.3406764391789</v>
+        <v>809.1011884638457</v>
       </c>
       <c r="L38" t="n">
-        <v>1226.451937043414</v>
+        <v>794.485584576661</v>
       </c>
       <c r="M38" t="n">
-        <v>1732.134985435348</v>
+        <v>1300.168632968594</v>
       </c>
       <c r="N38" t="n">
-        <v>2342.268080808026</v>
+        <v>1910.301728341273</v>
       </c>
       <c r="O38" t="n">
-        <v>2326.729999999944</v>
+        <v>2675.571728341328</v>
       </c>
       <c r="P38" t="n">
-        <v>3092</v>
+        <v>2660.033647533246</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
@@ -7210,7 +7210,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y38" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="39">
@@ -7241,28 +7241,28 @@
         <v>61.84</v>
       </c>
       <c r="I39" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>185.796520175299</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>663.0793362696824</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>1060.961905939123</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M39" t="n">
-        <v>1147.042447681983</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N39" t="n">
-        <v>1280.322732289551</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O39" t="n">
-        <v>1519.36518397327</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P39" t="n">
-        <v>1631.894528442776</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q39" t="n">
         <v>1631.894528442776</v>
@@ -7338,7 +7338,7 @@
         <v>1011.831843630703</v>
       </c>
       <c r="O40" t="n">
-        <v>658.8565263791725</v>
+        <v>901.5240037917935</v>
       </c>
       <c r="P40" t="n">
         <v>501.0715822480788</v>
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>144.0740160054425</v>
+        <v>300.7032103464585</v>
       </c>
       <c r="C41" t="n">
-        <v>144.0740160054425</v>
+        <v>61.84</v>
       </c>
       <c r="D41" t="n">
-        <v>144.0740160054425</v>
+        <v>61.84</v>
       </c>
       <c r="E41" t="n">
-        <v>144.0740160054425</v>
+        <v>61.84</v>
       </c>
       <c r="F41" t="n">
         <v>61.84</v>
@@ -7402,19 +7402,19 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K41" t="n">
-        <v>453.1491130376558</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L41" t="n">
-        <v>764.0617564435712</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="M41" t="n">
-        <v>1274.910585172506</v>
+        <v>1282.395195076803</v>
       </c>
       <c r="N41" t="n">
-        <v>1888.130904947269</v>
+        <v>1895.615514851567</v>
       </c>
       <c r="O41" t="n">
         <v>2653.400904947332</v>
@@ -7481,43 +7481,43 @@
         <v>61.84</v>
       </c>
       <c r="J42" t="n">
-        <v>351.8255811531334</v>
+        <v>396.666520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>751.8883972475169</v>
+        <v>796.7293362696823</v>
       </c>
       <c r="L42" t="n">
-        <v>1234.108858842717</v>
+        <v>1225.091634084787</v>
       </c>
       <c r="M42" t="n">
-        <v>1531.059400585576</v>
+        <v>1522.042175827647</v>
       </c>
       <c r="N42" t="n">
-        <v>1875.209685193144</v>
+        <v>1866.192460435215</v>
       </c>
       <c r="O42" t="n">
-        <v>2325.122136876863</v>
+        <v>2316.104912118933</v>
       </c>
       <c r="P42" t="n">
-        <v>2648.52148134637</v>
+        <v>2639.50425658844</v>
       </c>
       <c r="Q42" t="n">
-        <v>2688.043008906795</v>
+        <v>2679.025784148865</v>
       </c>
       <c r="R42" t="n">
-        <v>2350.392708611462</v>
+        <v>2341.375483853532</v>
       </c>
       <c r="S42" t="n">
-        <v>2094.267456121956</v>
+        <v>2085.250231364026</v>
       </c>
       <c r="T42" t="n">
-        <v>1899.966683174972</v>
+        <v>1890.949458417042</v>
       </c>
       <c r="U42" t="n">
-        <v>1710.865309679834</v>
+        <v>1701.848084921904</v>
       </c>
       <c r="V42" t="n">
-        <v>1507.319181203551</v>
+        <v>1498.301956445621</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="C43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="D43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="E43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="F43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="G43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="H43" t="n">
         <v>61.84</v>
@@ -7590,22 +7590,22 @@
         <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>64.78567915880487</v>
+        <v>61.84</v>
       </c>
       <c r="U43" t="n">
-        <v>75.34788872596938</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="V43" t="n">
-        <v>75.34788872596938</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="W43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="X43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="Y43" t="n">
-        <v>61.84</v>
+        <v>77.77043040567538</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>672.5796821712861</v>
+        <v>991.066662501746</v>
       </c>
       <c r="C44" t="n">
-        <v>407.4538455622013</v>
+        <v>725.9408258926612</v>
       </c>
       <c r="D44" t="n">
-        <v>181.8587387542722</v>
+        <v>500.3457190847322</v>
       </c>
       <c r="E44" t="n">
-        <v>181.8587387542722</v>
+        <v>280.7868406939558</v>
       </c>
       <c r="F44" t="n">
-        <v>61.84</v>
+        <v>280.7868406939558</v>
       </c>
       <c r="G44" t="n">
         <v>61.84</v>
@@ -7645,16 +7645,16 @@
         <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>1536.816366347868</v>
+        <v>1529.331756443634</v>
       </c>
       <c r="M44" t="n">
-        <v>2047.665195076803</v>
+        <v>2040.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>2047.665195076803</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2047.665195076803</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7672,19 +7672,19 @@
         <v>2312.8057087281</v>
       </c>
       <c r="U44" t="n">
-        <v>2312.8057087281</v>
+        <v>1845.91551019415</v>
       </c>
       <c r="V44" t="n">
-        <v>1865.481441892924</v>
+        <v>1398.591243358974</v>
       </c>
       <c r="W44" t="n">
-        <v>1409.548637871765</v>
+        <v>1289.045766497276</v>
       </c>
       <c r="X44" t="n">
-        <v>1000.173048517555</v>
+        <v>1289.045766497276</v>
       </c>
       <c r="Y44" t="n">
-        <v>672.5796821712861</v>
+        <v>1289.045766497276</v>
       </c>
     </row>
     <row r="45">
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1028.890452379605</v>
+        <v>820.2747032474441</v>
       </c>
       <c r="C45" t="n">
-        <v>853.031954959888</v>
+        <v>644.4162058277277</v>
       </c>
       <c r="D45" t="n">
-        <v>690.4686348611986</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="E45" t="n">
         <v>533.2240922128019</v>
@@ -7718,52 +7718,52 @@
         <v>61.84</v>
       </c>
       <c r="J45" t="n">
-        <v>370.9265201752989</v>
+        <v>227.1288148239817</v>
       </c>
       <c r="K45" t="n">
-        <v>745.2493362696823</v>
+        <v>601.4516309183651</v>
       </c>
       <c r="L45" t="n">
-        <v>1201.729797864882</v>
+        <v>1057.932092513565</v>
       </c>
       <c r="M45" t="n">
-        <v>1472.940339607742</v>
+        <v>1329.142634256425</v>
       </c>
       <c r="N45" t="n">
-        <v>1625.041306606297</v>
+        <v>1647.552918863993</v>
       </c>
       <c r="O45" t="n">
-        <v>2049.213758290016</v>
+        <v>2071.725370547712</v>
       </c>
       <c r="P45" t="n">
-        <v>2346.873102759523</v>
+        <v>2369.384715017219</v>
       </c>
       <c r="Q45" t="n">
-        <v>2360.654630319948</v>
+        <v>2383.166242577644</v>
       </c>
       <c r="R45" t="n">
-        <v>2360.654630319948</v>
+        <v>2383.166242577644</v>
       </c>
       <c r="S45" t="n">
-        <v>2360.654630319948</v>
+        <v>2383.166242577644</v>
       </c>
       <c r="T45" t="n">
-        <v>2140.091231110338</v>
+        <v>2162.602843368034</v>
       </c>
       <c r="U45" t="n">
-        <v>1924.727231352574</v>
+        <v>1947.23884361027</v>
       </c>
       <c r="V45" t="n">
-        <v>1694.918476613664</v>
+        <v>1717.43008887136</v>
       </c>
       <c r="W45" t="n">
-        <v>1678.194178498644</v>
+        <v>1469.578429366483</v>
       </c>
       <c r="X45" t="n">
-        <v>1442.979290169969</v>
+        <v>1234.363541037809</v>
       </c>
       <c r="Y45" t="n">
-        <v>1228.442529800137</v>
+        <v>1019.826780667976</v>
       </c>
     </row>
     <row r="46">
@@ -7797,43 +7797,43 @@
         <v>72.10287893608292</v>
       </c>
       <c r="J46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="K46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="L46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="M46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="N46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="O46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="P46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="Q46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="R46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="S46" t="n">
-        <v>143.672759546362</v>
+        <v>103.9022445577664</v>
       </c>
       <c r="T46" t="n">
-        <v>120.4156216612533</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="U46" t="n">
-        <v>156.0968142995399</v>
+        <v>116.3262993109443</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="W46" t="n">
         <v>104.0330566683016</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>326.9162243030381</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>884.2478695740924</v>
+        <v>852.6958452008894</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
-        <v>205.219884327485</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,22 +8201,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>163.0335112078408</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>844.2414264171106</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409606</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P5" t="n">
         <v>814.2870600406815</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>8.268880716849676</v>
       </c>
       <c r="L8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698307</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>163.320571248526</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8687,7 +8687,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>815.1849144666769</v>
       </c>
       <c r="O11" t="n">
         <v>70.24786957409245</v>
@@ -8696,7 +8696,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>334.3735652474629</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8930,10 +8930,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>114.0702823596368</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>334.3735652474629</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,10 +9152,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>231.79875049407</v>
       </c>
       <c r="P17" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>627.0604808351362</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>334.3735652474629</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>718.0600319897761</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>884.2478695740924</v>
+        <v>184.0310918930479</v>
       </c>
       <c r="P23" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,22 +9863,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>603.4970285185419</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>110.4553161506355</v>
+        <v>843.247869574119</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407081</v>
       </c>
       <c r="Q26" t="n">
         <v>172.8226843274854</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>314.0531751575203</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,10 +10112,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741263</v>
       </c>
       <c r="P29" t="n">
-        <v>370.4651176751361</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10340,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>375.2922462381547</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,10 +10349,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741345</v>
+        <v>445.5401158122531</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407226</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>50.42570624509131</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>465.9428479982005</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>662.5632917884309</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741409</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407308</v>
+        <v>773.2870600407299</v>
       </c>
       <c r="Q35" t="n">
-        <v>188.2053843274865</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>50.42570624509142</v>
+        <v>88.72186530119929</v>
       </c>
       <c r="K38" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>465.9428479981929</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,13 +10823,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741481</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407381</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>188.2053843274866</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>314.0531751574904</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,7 +11060,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>843.2478695741563</v>
+        <v>835.6876575496134</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11288,19 +11288,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>612.1413124351556</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22700,10 +22700,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.662449696443232</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>29.21007785422825</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>5.662449696447723</v>
+        <v>5.662449696446828</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785423092</v>
+        <v>29.21007785422279</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23235,10 +23235,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>134.3161930315095</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>15.78260154749196</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23283,7 +23283,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23411,13 +23411,13 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>153.4024400718014</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N13" t="n">
-        <v>346.1850752716849</v>
+        <v>5.408275783157251</v>
       </c>
       <c r="O13" t="n">
         <v>415.445564079015</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>85.17769029970491</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>51.14877515391792</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -23651,7 +23651,7 @@
         <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>269.6316114025499</v>
+        <v>215.8903306724398</v>
       </c>
       <c r="N16" t="n">
         <v>320.1850752716849</v>
@@ -23663,10 +23663,10 @@
         <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23748,10 +23748,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4306086145855375</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -23885,10 +23885,10 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
-        <v>144.5476281577792</v>
+        <v>8.386241106630735</v>
       </c>
       <c r="M19" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>292.1850752716849</v>
@@ -23897,13 +23897,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>108.2004986247733</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -24134,13 +24134,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R22" t="n">
-        <v>69.8091295274528</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24180,7 +24180,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4306086145860064</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24338,7 +24338,7 @@
         <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24359,28 +24359,28 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>108.2004986247733</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>83.37347970285543</v>
+        <v>46.73829239718017</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24411,16 +24411,16 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>220.4020581374557</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>178.7573722870162</v>
@@ -24459,13 +24459,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>309.8068086500135</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24566,22 +24566,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>17.4714520478421</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24608,7 +24608,7 @@
         <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
         <v>500.839266425598</v>
@@ -24635,7 +24635,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24651,19 +24651,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>112.3496867274454</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,16 +24702,16 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>35.06290239760585</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24809,16 +24809,16 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24830,10 +24830,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>169.700807021641</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
         <v>295.6316114025499</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24872,7 +24872,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -25073,25 +25073,25 @@
         <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>106.4066273183019</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.322948915185336</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25316,16 +25316,16 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>240.2408026384947</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>326.3973665406309</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
         <v>71.37347970285543</v>
@@ -25553,10 +25553,10 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>240.2408026384947</v>
       </c>
       <c r="P40" t="n">
-        <v>240.2408026384948</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>155.0629023976058</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
@@ -25605,7 +25605,7 @@
         <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>110.4779528626238</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>190.7573722870162</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>128.5393902319699</v>
+        <v>137.4664427423205</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25769,7 +25769,7 @@
         <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>15.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25839,13 +25839,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>99.07107734128236</v>
+        <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>221.0096587035274</v>
@@ -25887,19 +25887,19 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>462.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>342.9234538878665</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25915,10 +25915,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>50.85749441892609</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>228.816087775958</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26051,7 +26051,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>863514.6693194399</v>
+        <v>863514.66931944</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2957026.079543485</v>
+        <v>2957026.079543486</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3630897.530649927</v>
+        <v>3630897.530649928</v>
       </c>
     </row>
     <row r="7">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5032926.922117087</v>
+        <v>5032926.922117088</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5733941.617850666</v>
+        <v>5733941.617850667</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6370572.015384999</v>
+        <v>6370572.015385002</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7010756.110697111</v>
+        <v>7010756.110697112</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7717062.218147174</v>
+        <v>7717062.218147176</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8422027.802331286</v>
+        <v>8422027.802331287</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9126993.386515401</v>
+        <v>9126993.386515403</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9746729.006854568</v>
+        <v>9746729.00685457</v>
       </c>
     </row>
     <row r="16">
@@ -26269,22 +26269,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1478944.298195309</v>
+        <v>1478944.29819531</v>
       </c>
       <c r="C2" t="n">
         <v>1478944.29819531</v>
       </c>
       <c r="D2" t="n">
-        <v>1478944.29819531</v>
+        <v>1478944.298195309</v>
       </c>
       <c r="E2" t="n">
         <v>1323084.101908756</v>
       </c>
       <c r="F2" t="n">
-        <v>1377041.660956642</v>
+        <v>1377041.660956641</v>
       </c>
       <c r="G2" t="n">
-        <v>1432508.29128167</v>
+        <v>1432508.291281669</v>
       </c>
       <c r="H2" t="n">
         <v>1432508.291281674</v>
@@ -26293,25 +26293,25 @@
         <v>1432508.29128167</v>
       </c>
       <c r="J2" t="n">
+        <v>1308202.281724756</v>
+      </c>
+      <c r="K2" t="n">
         <v>1308202.281724757</v>
       </c>
-      <c r="K2" t="n">
-        <v>1308202.281724756</v>
-      </c>
       <c r="L2" t="n">
+        <v>1440581.845941442</v>
+      </c>
+      <c r="M2" t="n">
         <v>1440581.845941441</v>
       </c>
-      <c r="M2" t="n">
-        <v>1440581.84594144</v>
-      </c>
       <c r="N2" t="n">
-        <v>1440581.845941442</v>
+        <v>1440581.845941441</v>
       </c>
       <c r="O2" t="n">
-        <v>1269155.597801758</v>
+        <v>1269155.597801759</v>
       </c>
       <c r="P2" t="n">
-        <v>1183786.739426839</v>
+        <v>1183786.73942684</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575615.820517953</v>
+        <v>580502.3723909451</v>
       </c>
       <c r="C4" t="n">
-        <v>573863.9117786936</v>
+        <v>578750.4636516855</v>
       </c>
       <c r="D4" t="n">
-        <v>572109.6264658828</v>
+        <v>576996.1783388748</v>
       </c>
       <c r="E4" t="n">
-        <v>493887.8206072089</v>
+        <v>498724.2862854869</v>
       </c>
       <c r="F4" t="n">
-        <v>518162.4364012047</v>
+        <v>522998.9020794826</v>
       </c>
       <c r="G4" t="n">
-        <v>542951.8445255278</v>
+        <v>547788.3102038057</v>
       </c>
       <c r="H4" t="n">
-        <v>541278.9095854331</v>
+        <v>546115.375263711</v>
       </c>
       <c r="I4" t="n">
-        <v>539603.6392010038</v>
+        <v>544440.1048792817</v>
       </c>
       <c r="J4" t="n">
-        <v>483069.4589672089</v>
+        <v>487781.687779115</v>
       </c>
       <c r="K4" t="n">
-        <v>481604.7173132672</v>
+        <v>486316.9461251732</v>
       </c>
       <c r="L4" t="n">
-        <v>543419.7365500288</v>
+        <v>548178.8299014306</v>
       </c>
       <c r="M4" t="n">
-        <v>541689.6178484763</v>
+        <v>546448.7111998776</v>
       </c>
       <c r="N4" t="n">
-        <v>539957.011523924</v>
+        <v>544716.1048753255</v>
       </c>
       <c r="O4" t="n">
-        <v>457615.9305970518</v>
+        <v>462328.1594089579</v>
       </c>
       <c r="P4" t="n">
-        <v>416810.1932019159</v>
+        <v>421522.422013822</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>533681.6776773564</v>
+        <v>528795.1258043651</v>
       </c>
       <c r="C6" t="n">
-        <v>821961.5864166163</v>
+        <v>817075.0345436244</v>
       </c>
       <c r="D6" t="n">
-        <v>823715.8717294275</v>
+        <v>818829.3198564346</v>
       </c>
       <c r="E6" t="n">
-        <v>580789.5563015473</v>
+        <v>575953.0906232696</v>
       </c>
       <c r="F6" t="n">
-        <v>767486.705555437</v>
+        <v>762650.2398771584</v>
       </c>
       <c r="G6" t="n">
-        <v>794209.9957561421</v>
+        <v>789373.5300778635</v>
       </c>
       <c r="H6" t="n">
-        <v>818282.9306962412</v>
+        <v>813446.4650179629</v>
       </c>
       <c r="I6" t="n">
-        <v>819958.2010806658</v>
+        <v>815121.7354023879</v>
       </c>
       <c r="J6" t="n">
-        <v>350322.8977575479</v>
+        <v>345610.6689456408</v>
       </c>
       <c r="K6" t="n">
-        <v>739883.639411489</v>
+        <v>735171.4105995833</v>
       </c>
       <c r="L6" t="n">
-        <v>750499.6303914124</v>
+        <v>745740.5370400113</v>
       </c>
       <c r="M6" t="n">
-        <v>827429.7490929642</v>
+        <v>822670.6557415631</v>
       </c>
       <c r="N6" t="n">
-        <v>829162.3554175177</v>
+        <v>824403.2620661156</v>
       </c>
       <c r="O6" t="n">
-        <v>672234.570204706</v>
+        <v>667522.341392801</v>
       </c>
       <c r="P6" t="n">
-        <v>704257.2432249233</v>
+        <v>699545.0144130177</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -27493,7 +27493,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>307.3903671255642</v>
+        <v>306.4306086145855</v>
       </c>
       <c r="W2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.01010979890282</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>273.8338555691327</v>
       </c>
     </row>
     <row r="4">
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27600,25 +27600,25 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>351.5958765036442</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
-      </c>
       <c r="U4" t="n">
-        <v>258.963080349934</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27657,10 +27657,10 @@
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.51176829727012</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
@@ -27679,16 +27679,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27733,7 +27733,7 @@
         <v>400</v>
       </c>
       <c r="W5" t="n">
-        <v>400</v>
+        <v>56.51176829727035</v>
       </c>
       <c r="X5" t="n">
         <v>400</v>
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27761,10 +27761,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>207.6501538294815</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>76.45355315257606</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>400</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,19 +27828,19 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>370.8820140359639</v>
+      </c>
+      <c r="C7" t="n">
         <v>400</v>
       </c>
-      <c r="C7" t="n">
-        <v>272.7252466480447</v>
-      </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>318.8985472022821</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27891,7 +27891,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27919,7 +27919,7 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>56.51176829727031</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,16 +27958,16 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
+        <v>56.51176829727007</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>400</v>
-      </c>
-      <c r="T8" t="n">
-        <v>400</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27995,7 +27995,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>115.3536407070569</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28043,13 +28043,13 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>284.9464728384898</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28080,13 +28080,13 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28122,13 +28122,13 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>195.9005525854242</v>
+        <v>199.7663441787101</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>19.1168712588389</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>19.11687125883863</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28481,7 +28481,7 @@
         <v>251</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>251</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>251</v>
+        <v>166.1982915220774</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
@@ -28499,13 +28499,13 @@
         <v>251</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>251</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" t="n">
-        <v>200.0719056307292</v>
+        <v>251</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28721,25 +28721,25 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>155.6705902671031</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>155.6705902671032</v>
+      </c>
+      <c r="P18" t="n">
         <v>279</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>279</v>
@@ -28958,25 +28958,25 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>279</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>155.6705902671034</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29198,7 +29198,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29210,7 +29210,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -29429,7 +29429,7 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
@@ -29444,10 +29444,10 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>26.99048536749072</v>
+        <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29669,13 +29669,13 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>19.11687125883917</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M30" t="n">
         <v>225</v>
@@ -29903,22 +29903,22 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
+        <v>227.015861157829</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>291</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>227.0158611578289</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -30027,7 +30027,7 @@
         <v>291</v>
       </c>
       <c r="X34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="Y34" t="n">
         <v>291</v>
@@ -30043,7 +30043,7 @@
         <v>291</v>
       </c>
       <c r="C35" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="D35" t="n">
         <v>291</v>
@@ -30109,7 +30109,7 @@
         <v>291</v>
       </c>
       <c r="Y35" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="36">
@@ -30140,16 +30140,16 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
+        <v>227.0158611578289</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>291</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
-        <v>227.0158611578289</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -30295,7 +30295,7 @@
         <v>291</v>
       </c>
       <c r="H38" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30346,7 +30346,7 @@
         <v>291</v>
       </c>
       <c r="Y38" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39">
@@ -30377,31 +30377,31 @@
         <v>291</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>227.0158611578287</v>
+      </c>
+      <c r="Q39" t="n">
         <v>291</v>
-      </c>
-      <c r="L39" t="n">
-        <v>127.810210176001</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>291</v>
@@ -30617,13 +30617,13 @@
         <v>213</v>
       </c>
       <c r="J42" t="n">
-        <v>167.7061221998327</v>
+        <v>213</v>
       </c>
       <c r="K42" t="n">
         <v>213</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>158.5978143635403</v>
       </c>
       <c r="M42" t="n">
         <v>213</v>
@@ -30726,10 +30726,10 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>213</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>161.6272898271494</v>
+        <v>180.6940671650082</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
@@ -30854,7 +30854,7 @@
         <v>187</v>
       </c>
       <c r="J45" t="n">
-        <v>187</v>
+        <v>41.74979257442701</v>
       </c>
       <c r="K45" t="n">
         <v>187</v>
@@ -30866,7 +30866,7 @@
         <v>187</v>
       </c>
       <c r="N45" t="n">
-        <v>19.01079029392637</v>
+        <v>187</v>
       </c>
       <c r="O45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>187</v>
       </c>
       <c r="J46" t="n">
-        <v>107.5617575331594</v>
+        <v>67.38952017094161</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -34746,10 +34746,10 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34886,25 +34886,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>63.07510270250117</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>108.0046890754761</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34943,10 +34943,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -34995,7 +34995,7 @@
         <v>814</v>
       </c>
       <c r="O5" t="n">
-        <v>814.0000000000036</v>
+        <v>814</v>
       </c>
       <c r="P5" t="n">
         <v>814</v>
@@ -35114,19 +35114,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>83.76821369888529</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
@@ -35138,7 +35138,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>283.6295983663744</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35177,7 +35177,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35220,10 +35220,10 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>814</v>
@@ -35366,13 +35366,13 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35408,13 +35408,13 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>44.94216131096627</v>
+        <v>48.8079529042522</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -35466,7 +35466,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35475,7 +35475,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>161.5508809199775</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>293.2082466075259</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734918</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L14" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35709,10 +35709,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>113.7832223189554</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,7 +35767,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
         <v>125.2086062376757</v>
@@ -35776,7 +35776,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>440.2896668707643</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
@@ -35785,13 +35785,13 @@
         <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>113.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.99264054024963</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="P17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,10 +36007,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>280.8791965047788</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36022,10 +36022,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>397.1276121698496</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
         <v>105.9207349095204</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>556.8126112610438</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="R20" t="n">
         <v>5.512089101654111e-11</v>
@@ -36244,25 +36244,25 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M21" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N21" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757578</v>
       </c>
       <c r="O21" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>269.3365947817566</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>240.8110739199409</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>814</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="P23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36484,7 +36484,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36496,7 +36496,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
@@ -36642,22 +36642,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>603.4970285185419</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>40.20744657654306</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
@@ -36730,10 +36730,10 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>161.6170354761456</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>314.0531751575203</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,10 +36891,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="P29" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,13 +36955,13 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M30" t="n">
         <v>311.9500421645043</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320760657</v>
+        <v>727.1079320763263</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>73.87361410865147</v>
+        <v>9.889475266480432</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37204,7 +37204,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>361.6424112664837</v>
+        <v>425.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37313,7 +37313,7 @@
         <v>64.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>43.55635456989245</v>
+        <v>43.55635456991639</v>
       </c>
       <c r="Y34" t="n">
         <v>3.534647150537637</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760333</v>
+        <v>772.9999999999998</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320759846</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,16 +37426,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>73.87361410865147</v>
+        <v>9.889475266480403</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
-        <v>191.1038546407913</v>
+        <v>482.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>501.1072365065158</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320759941</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.1079320760183</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,16 +37663,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>482.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>401.901585524688</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
@@ -37684,10 +37684,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>340.6818656724819</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>314.0531751574904</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,7 +37839,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>773.0000000000639</v>
+        <v>765.439787975521</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37903,13 +37903,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>292.9147284375085</v>
+        <v>338.2086062376757</v>
       </c>
       <c r="K42" t="n">
         <v>404.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>487.091375348687</v>
+        <v>432.6891897122273</v>
       </c>
       <c r="M42" t="n">
         <v>299.9500421645043</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.975433493742287</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>10.66889855269143</v>
+        <v>29.73567589055027</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38067,19 +38067,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>772.9999999999999</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>611.854252394474</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>312.2086062376757</v>
+        <v>166.9583988121027</v>
       </c>
       <c r="K45" t="n">
         <v>378.1038546407913</v>
@@ -38152,7 +38152,7 @@
         <v>273.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>153.6373404025812</v>
+        <v>321.6265501086548</v>
       </c>
       <c r="O45" t="n">
         <v>428.4570219027464</v>
@@ -38219,7 +38219,7 @@
         <v>10.36654437988173</v>
       </c>
       <c r="J46" t="n">
-        <v>72.29280869725164</v>
+        <v>32.12057133503384</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
